--- a/Employee_Reports_wi52/Billy Jim Morelos Q0281.xlsx
+++ b/Employee_Reports_wi52/Billy Jim Morelos Q0281.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -927,53 +927,53 @@
       <c r="K10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Bin Hoist S-Type (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-011</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>29-Sep-2024</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>29-Sep-2026</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1598,11 +1598,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1684,11 +1684,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1721,11 +1721,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
